--- a/mutasi bca.xlsx
+++ b/mutasi bca.xlsx
@@ -1,31 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21001"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{84545125-2D58-4A7D-8B6B-5AF6179A9260}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6820" xr2:uid="{48DA69CA-61C0-4D94-BBC0-13CA88C2F852}"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="179021"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="101">
   <si>
     <t>MUTASI REKENING MANDIRI VERIFIKASI</t>
   </si>
@@ -333,86 +323,104 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="d\ mmmm\ yyyy\ h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="dd\ mmm\ yyyy\ h:mm:ss"/>
     <numFmt numFmtId="166" formatCode="dd\ mmmm\ yyyy\ h:mm:ss"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="24"/>
       <color rgb="FF1C4587"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="18"/>
       <color rgb="FF1C4587"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="16"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="8"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="9"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -460,140 +468,140 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="51">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="14" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="5" numFmtId="49" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="7" numFmtId="164" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="7" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="7" numFmtId="4" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="7" numFmtId="49" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="7" numFmtId="165" fillId="4" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="7" numFmtId="4" fillId="4" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="7" numFmtId="4" fillId="4" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="7" numFmtId="49" fillId="4" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="7" numFmtId="165" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="7" numFmtId="4" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="7" numFmtId="164" fillId="4" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="8" numFmtId="165" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="4" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="4" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="49" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="165" fillId="5" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="4" fillId="5" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="4" fillId="5" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="49" fillId="5" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="165" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="4" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="4" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="49" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="166" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="165" fillId="4" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="4" fillId="4" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="4" fillId="4" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="49" fillId="4" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="9" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="166" fillId="5" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="4" fillId="5" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="166" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="165" fillId="5" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="4" fillId="5" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="49" fillId="5" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -603,18 +611,29 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFCE5CD"/>
+          <bgColor rgb="FFFCE5CD"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9FC5E8"/>
+          <bgColor rgb="FF9FC5E8"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFA4C2F4"/>
           <bgColor rgb="FFA4C2F4"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
+      <border/>
     </dxf>
     <dxf>
       <fill>
@@ -623,25 +642,10 @@
           <bgColor rgb="FFF4CCCC"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9FC5E8"/>
-          <bgColor rgb="FF9FC5E8"/>
-        </patternFill>
-      </fill>
+      <border/>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
@@ -688,7 +692,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -740,7 +744,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -801,151 +805,178 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB9F1270-1558-4D45-BF3B-60D9C2447F39}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:E60"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="30" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" customHeight="1" ht="30">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -954,7 +985,7 @@
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:5" ht="23.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" customHeight="1" ht="23.5">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -963,14 +994,14 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5">
       <c r="A3" s="5"/>
       <c r="B3" s="6"/>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
     </row>
-    <row r="4" spans="1:5" ht="21" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" customHeight="1" ht="21">
       <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
@@ -979,14 +1010,14 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5">
       <c r="A5" s="5"/>
       <c r="B5" s="6"/>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5">
       <c r="A6" s="10" t="s">
         <v>3</v>
       </c>
@@ -1003,16 +1034,16 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5">
       <c r="A7" s="9"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5">
       <c r="A8" s="12">
-        <v>46204.384652777779</v>
+        <v>46235.384652778</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>8</v>
@@ -1027,9 +1058,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5">
       <c r="A9" s="16">
-        <v>46204.386099537034</v>
+        <v>46235.386099537</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>10</v>
@@ -1041,12 +1072,12 @@
         <v>11</v>
       </c>
       <c r="E9" s="18">
-        <v>8044928.4900000002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+        <v>8044928.49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="20">
-        <v>46204.409456018519</v>
+        <v>46235.409456019</v>
       </c>
       <c r="B10" s="21" t="s">
         <v>12</v>
@@ -1058,12 +1089,12 @@
         <v>13</v>
       </c>
       <c r="E10" s="14">
-        <v>8254928.4900000002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+        <v>8254928.49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="22">
-        <v>46204.479780092595</v>
+        <v>46235.479780093</v>
       </c>
       <c r="B11" s="17" t="s">
         <v>14</v>
@@ -1078,9 +1109,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5">
       <c r="A12" s="23">
-        <v>46204.535138888888</v>
+        <v>46235.535138889</v>
       </c>
       <c r="B12" s="24" t="s">
         <v>16</v>
@@ -1095,9 +1126,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5">
       <c r="A13" s="27">
-        <v>46204.554386574076</v>
+        <v>46235.554386574</v>
       </c>
       <c r="B13" s="28" t="s">
         <v>18</v>
@@ -1112,9 +1143,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5">
       <c r="A14" s="31">
-        <v>46204.575729166667</v>
+        <v>46235.575729167</v>
       </c>
       <c r="B14" s="32" t="s">
         <v>19</v>
@@ -1126,12 +1157,12 @@
         <v>20</v>
       </c>
       <c r="E14" s="33">
-        <v>8830112.4900000002</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+        <v>8830112.49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="27">
-        <v>46204.603333333333</v>
+        <v>46235.603333333</v>
       </c>
       <c r="B15" s="28" t="s">
         <v>21</v>
@@ -1143,12 +1174,12 @@
         <v>20</v>
       </c>
       <c r="E15" s="29">
-        <v>8845112.4900000002</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+        <v>8845112.49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" s="35">
-        <v>46204.615474537037</v>
+        <v>46235.615474537</v>
       </c>
       <c r="B16" s="32" t="s">
         <v>22</v>
@@ -1163,9 +1194,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5">
       <c r="A17" s="36">
-        <v>46204.615486111114</v>
+        <v>46235.615486111</v>
       </c>
       <c r="B17" s="37" t="s">
         <v>24</v>
@@ -1177,12 +1208,12 @@
         <v>25</v>
       </c>
       <c r="E17" s="38">
-        <v>8935112.4900000002</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+        <v>8935112.49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="35">
-        <v>46204.625</v>
+        <v>46235.625</v>
       </c>
       <c r="B18" s="40" t="s">
         <v>26</v>
@@ -1197,9 +1228,9 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5">
       <c r="A19" s="27">
-        <v>46204.661203703705</v>
+        <v>46235.661203704</v>
       </c>
       <c r="B19" s="28" t="s">
         <v>28</v>
@@ -1214,9 +1245,9 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5">
       <c r="A20" s="31">
-        <v>46204.749421296299</v>
+        <v>46235.749421296</v>
       </c>
       <c r="B20" s="32" t="s">
         <v>30</v>
@@ -1231,9 +1262,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5">
       <c r="A21" s="31">
-        <v>46204.777268518519</v>
+        <v>46235.777268519</v>
       </c>
       <c r="B21" s="32" t="s">
         <v>32</v>
@@ -1245,10 +1276,10 @@
         <v>33</v>
       </c>
       <c r="E21" s="33">
-        <v>8880112.4900000002</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+        <v>8880112.49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="41" t="s">
         <v>34</v>
       </c>
@@ -1257,9 +1288,9 @@
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5">
       <c r="A23" s="27">
-        <v>46205.319432870368</v>
+        <v>46236.31943287</v>
       </c>
       <c r="B23" s="28" t="s">
         <v>35</v>
@@ -1274,9 +1305,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5">
       <c r="A24" s="31">
-        <v>46205.360347222224</v>
+        <v>46236.360347222</v>
       </c>
       <c r="B24" s="40" t="s">
         <v>37</v>
@@ -1288,12 +1319,12 @@
         <v>20</v>
       </c>
       <c r="E24" s="33">
-        <v>9210112.4900000002</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+        <v>9210112.49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" s="27">
-        <v>46205.37699074074</v>
+        <v>46236.376990741</v>
       </c>
       <c r="B25" s="43" t="s">
         <v>38</v>
@@ -1305,12 +1336,12 @@
         <v>55000</v>
       </c>
       <c r="E25" s="29">
-        <v>9265112.4900000002</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+        <v>9265112.49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" s="35">
-        <v>46205.39739583333</v>
+        <v>46236.397395833</v>
       </c>
       <c r="B26" s="32" t="s">
         <v>39</v>
@@ -1325,9 +1356,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5">
       <c r="A27" s="27">
-        <v>46205.397812499999</v>
+        <v>46236.3978125</v>
       </c>
       <c r="B27" s="28" t="s">
         <v>41</v>
@@ -1339,12 +1370,12 @@
         <v>42</v>
       </c>
       <c r="E27" s="29">
-        <v>9335112.4900000002</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+        <v>9335112.49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" s="31">
-        <v>46205.444432870368</v>
+        <v>46236.44443287</v>
       </c>
       <c r="B28" s="32" t="s">
         <v>43</v>
@@ -1359,9 +1390,9 @@
         <v>44</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5">
       <c r="A29" s="27">
-        <v>46205.497824074075</v>
+        <v>46236.497824074</v>
       </c>
       <c r="B29" s="28" t="s">
         <v>45</v>
@@ -1373,12 +1404,12 @@
         <v>46</v>
       </c>
       <c r="E29" s="29">
-        <v>9635112.4900000002</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+        <v>9635112.49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" s="31">
-        <v>46205.502592592595</v>
+        <v>46236.502592593</v>
       </c>
       <c r="B30" s="32" t="s">
         <v>47</v>
@@ -1390,12 +1421,12 @@
         <v>48</v>
       </c>
       <c r="E30" s="33">
-        <v>9760448.4900000002</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+        <v>9760448.49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" s="27">
-        <v>46205.507037037038</v>
+        <v>46236.507037037</v>
       </c>
       <c r="B31" s="28" t="s">
         <v>49</v>
@@ -1410,9 +1441,9 @@
         <v>10320448.49</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5">
       <c r="A32" s="35">
-        <v>46205.54</v>
+        <v>46236.54</v>
       </c>
       <c r="B32" s="32" t="s">
         <v>51</v>
@@ -1427,9 +1458,9 @@
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5">
       <c r="A33" s="27">
-        <v>46205.543946759259</v>
+        <v>46236.543946759</v>
       </c>
       <c r="B33" s="28" t="s">
         <v>53</v>
@@ -1444,9 +1475,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5">
       <c r="A34" s="31">
-        <v>46205.547048611108</v>
+        <v>46236.547048611</v>
       </c>
       <c r="B34" s="32" t="s">
         <v>55</v>
@@ -1461,9 +1492,9 @@
         <v>12125448.49</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5">
       <c r="A35" s="27">
-        <v>46205.547118055554</v>
+        <v>46236.547118056</v>
       </c>
       <c r="B35" s="28" t="s">
         <v>57</v>
@@ -1478,9 +1509,9 @@
         <v>12650644.49</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5">
       <c r="A36" s="31">
-        <v>46205.562175925923</v>
+        <v>46236.562175926</v>
       </c>
       <c r="B36" s="32" t="s">
         <v>59</v>
@@ -1495,9 +1526,9 @@
         <v>12900644.49</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5">
       <c r="A37" s="27">
-        <v>46205.568888888891</v>
+        <v>46236.568888889</v>
       </c>
       <c r="B37" s="28" t="s">
         <v>61</v>
@@ -1512,9 +1543,9 @@
         <v>13125689.49</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5">
       <c r="A38" s="31">
-        <v>46205.614571759259</v>
+        <v>46236.614571759</v>
       </c>
       <c r="B38" s="32" t="s">
         <v>63</v>
@@ -1529,9 +1560,9 @@
         <v>64</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5">
       <c r="A39" s="27">
-        <v>46205.62704861111</v>
+        <v>46236.627048611</v>
       </c>
       <c r="B39" s="28" t="s">
         <v>65</v>
@@ -1546,9 +1577,9 @@
         <v>13170689.49</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5">
       <c r="A40" s="31">
-        <v>46205.628611111111</v>
+        <v>46236.628611111</v>
       </c>
       <c r="B40" s="40" t="s">
         <v>67</v>
@@ -1563,9 +1594,9 @@
         <v>13200689.49</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5">
       <c r="A41" s="45">
-        <v>46205.75508101852</v>
+        <v>46236.755081019</v>
       </c>
       <c r="B41" s="28" t="s">
         <v>68</v>
@@ -1580,9 +1611,9 @@
         <v>69</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5">
       <c r="A42" s="31">
-        <v>46205.762083333335</v>
+        <v>46236.762083333</v>
       </c>
       <c r="B42" s="32" t="s">
         <v>70</v>
@@ -1597,9 +1628,9 @@
         <v>13675841.49</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5">
       <c r="A43" s="27">
-        <v>46205.763715277775</v>
+        <v>46236.763715278</v>
       </c>
       <c r="B43" s="28" t="s">
         <v>70</v>
@@ -1614,9 +1645,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5">
       <c r="A44" s="31">
-        <v>46205.769745370373</v>
+        <v>46236.76974537</v>
       </c>
       <c r="B44" s="32" t="s">
         <v>73</v>
@@ -1631,9 +1662,9 @@
         <v>13946218.49</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5">
       <c r="A45" s="27">
-        <v>46205.873807870368</v>
+        <v>46236.87380787</v>
       </c>
       <c r="B45" s="28" t="s">
         <v>75</v>
@@ -1648,7 +1679,7 @@
         <v>14846626.49</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5">
       <c r="A46" s="41" t="s">
         <v>34</v>
       </c>
@@ -1657,9 +1688,9 @@
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5">
       <c r="A47" s="45">
-        <v>46206.084467592591</v>
+        <v>46237.084467593</v>
       </c>
       <c r="B47" s="28" t="s">
         <v>77</v>
@@ -1674,9 +1705,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5">
       <c r="A48" s="31">
-        <v>46206.314085648148</v>
+        <v>46237.314085648</v>
       </c>
       <c r="B48" s="40" t="s">
         <v>79</v>
@@ -1691,9 +1722,9 @@
         <v>15086626.49</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5">
       <c r="A49" s="27">
-        <v>46206.392094907409</v>
+        <v>46237.392094907</v>
       </c>
       <c r="B49" s="28" t="s">
         <v>80</v>
@@ -1708,9 +1739,9 @@
         <v>81</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5">
       <c r="A50" s="31">
-        <v>46206.401226851849</v>
+        <v>46237.401226852</v>
       </c>
       <c r="B50" s="32" t="s">
         <v>82</v>
@@ -1725,9 +1756,9 @@
         <v>15146626.49</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5">
       <c r="A51" s="27">
-        <v>46206.411909722221</v>
+        <v>46237.411909722</v>
       </c>
       <c r="B51" s="28" t="s">
         <v>83</v>
@@ -1742,9 +1773,9 @@
         <v>15396626.49</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5">
       <c r="A52" s="31">
-        <v>46206.413738425923</v>
+        <v>46237.413738426</v>
       </c>
       <c r="B52" s="32" t="s">
         <v>84</v>
@@ -1759,9 +1790,9 @@
         <v>15676626.49</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5">
       <c r="A53" s="27">
-        <v>46206.415150462963</v>
+        <v>46237.415150463</v>
       </c>
       <c r="B53" s="28" t="s">
         <v>86</v>
@@ -1776,9 +1807,9 @@
         <v>15701626.49</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5">
       <c r="A54" s="31">
-        <v>46206.421018518522</v>
+        <v>46237.421018519</v>
       </c>
       <c r="B54" s="32" t="s">
         <v>88</v>
@@ -1793,9 +1824,9 @@
         <v>89</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5">
       <c r="A55" s="27">
-        <v>46206.433206018519</v>
+        <v>46237.433206019</v>
       </c>
       <c r="B55" s="28" t="s">
         <v>90</v>
@@ -1810,9 +1841,9 @@
         <v>15761626.49</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5">
       <c r="A56" s="31">
-        <v>46206.433564814812</v>
+        <v>46237.433564815</v>
       </c>
       <c r="B56" s="32" t="s">
         <v>92</v>
@@ -1827,9 +1858,9 @@
         <v>16011626.49</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5">
       <c r="A57" s="27">
-        <v>46206.465844907405</v>
+        <v>46237.465844907</v>
       </c>
       <c r="B57" s="28" t="s">
         <v>93</v>
@@ -1844,9 +1875,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5">
       <c r="A58" s="47">
-        <v>46206.478472222225</v>
+        <v>46237.478472222</v>
       </c>
       <c r="B58" s="24" t="s">
         <v>95</v>
@@ -1861,9 +1892,9 @@
         <v>96</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5">
       <c r="A59" s="48">
-        <v>46206.483356481483</v>
+        <v>46237.483356481</v>
       </c>
       <c r="B59" s="49" t="s">
         <v>97</v>
@@ -1878,9 +1909,9 @@
         <v>16151626.49</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5">
       <c r="A60" s="23">
-        <v>46206.485162037039</v>
+        <v>46237.485162037</v>
       </c>
       <c r="B60" s="24" t="s">
         <v>99</v>
@@ -1896,7 +1927,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells>
     <mergeCell ref="A46:E46"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="A4:B4"/>
@@ -1906,26 +1937,65 @@
     <mergeCell ref="D6:D7"/>
     <mergeCell ref="E6:E7"/>
   </mergeCells>
-  <conditionalFormatting sqref="A22:E22 B24:E24 A24:A25 A46:E46 A48:E48">
-    <cfRule type="expression" dxfId="3" priority="2">
+  <conditionalFormatting sqref="A22:E22">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>#REF!="BCA EDC"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>#REF!="MASUK OPERASIONAL"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B24:E24">
+    <cfRule type="expression" dxfId="0" priority="3">
+      <formula>#REF!="BCA EDC"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="4">
+      <formula>#REF!="MASUK OPERASIONAL"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A24:A25">
+    <cfRule type="expression" dxfId="0" priority="5">
+      <formula>#REF!="BCA EDC"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="6">
+      <formula>#REF!="MASUK OPERASIONAL"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A46:E46">
+    <cfRule type="expression" dxfId="0" priority="7">
+      <formula>#REF!="BCA EDC"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="8">
+      <formula>#REF!="MASUK OPERASIONAL"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A48:E48">
+    <cfRule type="expression" dxfId="0" priority="9">
+      <formula>#REF!="BCA EDC"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="10">
       <formula>#REF!="MASUK OPERASIONAL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8:E60">
-    <cfRule type="expression" dxfId="2" priority="4">
+    <cfRule type="expression" dxfId="2" priority="11">
+      <formula>#REF!="MASUK OPERASIONAL"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="12">
       <formula>#REF!="PENGELUARAN"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A22:E22 B24:E24 A24:A25 A46:E46 A48:E48">
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>#REF!="BCA EDC"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A8:E60">
-    <cfRule type="expression" dxfId="0" priority="3">
-      <formula>#REF!="MASUK OPERASIONAL"</formula>
-    </cfRule>
-  </conditionalFormatting>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
 </worksheet>
 </file>